--- a/diseases/d001/2010-2014.xlsx
+++ b/diseases/d001/2010-2014.xlsx
@@ -1209,9 +1209,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1602,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2197,9 +2191,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2789,9 +2780,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3233,9 +3221,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3825,9 +3810,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4417,9 +4399,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5009,9 +4988,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -5601,9 +5577,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6193,9 +6166,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -6785,9 +6755,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7377,9 +7344,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7969,9 +7933,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8561,9 +8522,6 @@
       <c r="O54" t="n">
         <v>0</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
@@ -8957,9 +8915,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -9549,9 +9504,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10141,9 +10093,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10733,9 +10682,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -11325,9 +11271,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11917,9 +11860,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -12509,9 +12449,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -13101,9 +13038,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -13693,9 +13627,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -14285,9 +14216,6 @@
       <c r="O92" t="n">
         <v>0</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0</v>
       </c>
@@ -14877,9 +14805,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15321,9 +15246,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -15913,9 +15835,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -16309,9 +16228,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16901,9 +16817,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -17345,9 +17258,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17789,9 +17699,6 @@
       <c r="O115" t="n">
         <v>0</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0</v>
       </c>
@@ -18233,9 +18140,6 @@
       <c r="O118" t="n">
         <v>0</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0</v>
       </c>
@@ -18677,9 +18581,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -19121,9 +19022,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -19565,9 +19463,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20009,9 +19904,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -20897,9 +20789,6 @@
       <c r="O136" t="n">
         <v>0</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0</v>
       </c>
@@ -21933,9 +21822,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -23265,9 +23151,6 @@
       <c r="O152" t="n">
         <v>0</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0</v>
       </c>
@@ -24449,9 +24332,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -24845,9 +24725,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -26029,9 +25906,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -27065,9 +26939,6 @@
       <c r="O177" t="n">
         <v>0</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0</v>
       </c>
@@ -28101,9 +27972,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -29285,9 +29153,6 @@
       <c r="O192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -30617,9 +30482,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -31653,9 +31515,6 @@
       <c r="O208" t="n">
         <v>0</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0</v>
       </c>
@@ -32837,9 +32696,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -34169,9 +34025,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -35205,9 +35058,6 @@
       <c r="O232" t="n">
         <v>0</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0</v>
       </c>
@@ -36537,9 +36387,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -37573,9 +37420,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -38609,9 +38453,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -39005,9 +38846,6 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0</v>
       </c>
@@ -40337,9 +40175,6 @@
       <c r="O266" t="n">
         <v>0</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0</v>
       </c>
@@ -41521,9 +41356,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -42705,9 +42537,6 @@
       <c r="O282" t="n">
         <v>0</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0</v>
       </c>
@@ -43741,9 +43570,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -44925,9 +44751,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -45961,9 +45784,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -47293,9 +47113,6 @@
       <c r="O313" t="n">
         <v>0</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0</v>
       </c>
@@ -48329,9 +48146,6 @@
       <c r="O320" t="n">
         <v>0</v>
       </c>
-      <c r="Q320" t="n">
-        <v>0</v>
-      </c>
       <c r="R320" t="n">
         <v>0</v>
       </c>
@@ -49365,9 +49179,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -50549,9 +50360,6 @@
       <c r="O335" t="n">
         <v>0</v>
       </c>
-      <c r="Q335" t="n">
-        <v>0</v>
-      </c>
       <c r="R335" t="n">
         <v>0</v>
       </c>
@@ -51583,9 +51391,6 @@
         <v>0</v>
       </c>
       <c r="O342" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q342" t="n">
         <v>0</v>
       </c>
       <c r="R342" t="n">
